--- a/PAMF_DIG F2 - monthly2026-07-12.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-12.xlsx
@@ -7568,7 +7568,7 @@
         <v>0.09</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-12.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-12.xlsx
@@ -8517,7 +8517,7 @@
         <v>0.09</v>
       </c>
       <c r="N111" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>0.09</v>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
